--- a/output/pdf_financials_xlsx/PCLO.xlsx
+++ b/output/pdf_financials_xlsx/PCLO.xlsx
@@ -3428,25 +3428,25 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>5.852995</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>24.486625</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>31.456069</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>35.13618</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>35.226154</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>35.620535</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>36.975137</v>
       </c>
     </row>
     <row r="93">
@@ -6046,7 +6046,11 @@
           <t>Reserves 12,13,14</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -7366,7 +7370,11 @@
           <t>Reserves 13,14,15</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
           <t>-</t>
@@ -8258,7 +8266,11 @@
           <t>Reserves 14,15,16</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -9330,7 +9342,11 @@
           <t>Reserves 13,14,15</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
@@ -10970,7 +10986,11 @@
           <t>Reserves (notes and 13, 14 and 15) 26,243,564</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/PCLO.xlsx
+++ b/output/pdf_financials_xlsx/PCLO.xlsx
@@ -768,25 +768,25 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.213534</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.585127</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.065582</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002374</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001828</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000176</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-1.2e-05</v>
       </c>
     </row>
     <row r="13">
@@ -1277,7 +1277,7 @@
         <v>-0.144395</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.028676</v>
+        <v>0.184858</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1285,19 +1285,19 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-43.755809</v>
+        <v>-43.690227</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-26.629693</v>
+        <v>-26.627319</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-14.516351</v>
+        <v>-14.514523</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-16.297635</v>
+        <v>-16.297459</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-11.369716</v>
+        <v>-11.369704</v>
       </c>
     </row>
     <row r="28">
@@ -1341,7 +1341,7 @@
         <v>-0.144395</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.32772</v>
+        <v>0.541254</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1349,19 +1349,19 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-42.276308</v>
+        <v>-42.210726</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-25.311098</v>
+        <v>-25.308724</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-14.063612</v>
+        <v>-14.061784</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-15.955979</v>
+        <v>-15.955803</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-11.13576</v>
+        <v>-11.135748</v>
       </c>
     </row>
     <row r="30">
@@ -1386,19 +1386,19 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-1592.97777586865</v>
+        <v>-1590.506636040238</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-1301.343137627905</v>
+        <v>-1301.221080947127</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-264.9254396284311</v>
+        <v>-264.8910043991571</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-1034.927150917562</v>
+        <v>-1034.915735311001</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-280.7348372567561</v>
+        <v>-280.7345347342479</v>
       </c>
     </row>
     <row r="31">
@@ -1484,10 +1484,8 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.087088</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>15.984352</v>
@@ -1502,13 +1500,13 @@
         <v>5.338371</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.172983</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.062179</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.054108</v>
       </c>
     </row>
     <row r="35">
@@ -1550,10 +1548,8 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.087088</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>15.996852</v>
@@ -1568,13 +1564,13 @@
         <v>5.629371</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.153</v>
+        <v>0.325983</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.062179</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.054108</v>
       </c>
     </row>
     <row r="37">
@@ -1964,13 +1960,13 @@
         <v>2.280859</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.305332</v>
+        <v>2.132349</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.373309</v>
+        <v>2.31113</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>1.419387</v>
+        <v>1.365279</v>
       </c>
     </row>
     <row r="49">
@@ -4419,22 +4415,22 @@
         <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.26153</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.261035</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.308217</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.302739</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.298062</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.041857</v>
       </c>
     </row>
     <row r="125">
@@ -4450,22 +4446,22 @@
         <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.26153</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.261035</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.308217</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.302739</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.298062</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.041857</v>
       </c>
     </row>
     <row r="126">
@@ -4910,7 +4906,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6338,7 +6334,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -12888,7 +12884,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -14478,7 +14478,11 @@
           <t>Lease payments 9</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -18590,7 +18594,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D248" t="inlineStr"/>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E248" t="inlineStr">
         <is>
           <t>-</t>
@@ -21124,7 +21132,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -24828,7 +24836,7 @@
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
@@ -25054,7 +25062,7 @@
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -26514,7 +26522,7 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
@@ -26798,7 +26806,7 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">

--- a/output/pdf_financials_xlsx/PCLO.xlsx
+++ b/output/pdf_financials_xlsx/PCLO.xlsx
@@ -2692,16 +2692,16 @@
         <v>0</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>0.150046</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>0.147945</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0</v>
+        <v>0.265318</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.041138</v>
       </c>
       <c r="I70" s="3" t="n">
         <v>0</v>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>0.150046</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>0.147945</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0</v>
+        <v>0.265318</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.041138</v>
       </c>
       <c r="I71" s="3" t="n">
         <v>0</v>
@@ -2857,16 +2857,16 @@
         <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>0.348108</v>
+        <v>0.198062</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.339055</v>
+        <v>0.19111</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.842715</v>
+        <v>0.577397</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>15.781189</v>
+        <v>15.740051</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>17.63542</v>
@@ -3025,25 +3025,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E80" s="3" t="n">
+        <v>0.005716692738223661</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.007655254269106262</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.04150790020256609</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>-0.02449232806311874</v>
       </c>
       <c r="I80" s="1" t="inlineStr">
         <is>
@@ -4131,16 +4123,16 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>1.402313</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.777089</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.17908</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -5506,7 +5498,11 @@
           <t>Current portion of lease obligations 8</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -6888,7 +6884,11 @@
           <t>Current portion of lease obligations 9</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -7094,7 +7094,11 @@
           <t>Non-current portion of lease obligations 9</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -9002,7 +9006,11 @@
           <t>Non-current portion of lease obligations 8</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>-</t>
@@ -10460,7 +10468,11 @@
           <t>Lease obligations (note 11) 147,597</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -10692,7 +10704,11 @@
           <t>Lease obligations (note 11) 1,424,850</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -12496,7 +12512,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -14034,7 +14054,11 @@
           <t>Proceeds from sale of marketable securities 5</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -15310,7 +15334,11 @@
           <t>Proceeds from sale of XPhyto marketable securities</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E189" t="inlineStr">
         <is>
           <t>-</t>
@@ -16408,7 +16436,11 @@
           <t>Proceeds from sale of XPhyto marketable securities 9</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr"/>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -21350,7 +21382,11 @@
           <t>Current income tax recovery</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -21408,7 +21444,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
